--- a/fhir/StructureDefinition-ehealth-goal.xlsx
+++ b/fhir/StructureDefinition-ehealth-goal.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -355,7 +355,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -530,7 +530,7 @@
     <t>Indicates the progression, or lack thereof, towards the goal against the target.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-achievement</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-achievement|4.0.1</t>
   </si>
   <si>
     <t>.statusCode achieved = complete sustaining = active</t>
@@ -554,7 +554,7 @@
     <t>Codes for grouping and sorting goals.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-category</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-category|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -580,7 +580,7 @@
     <t>The level of importance associated with a goal.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-priority</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-priority|4.0.1</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -660,7 +660,7 @@
     <t>Codes describing events that can trigger the initiation of a goal.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-start-event</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-start-event|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.planned</t>
@@ -903,7 +903,7 @@
     <t>The result of the goal; e.g. "25% increase in shoulder mobility", "Anxiety reduced to moderate levels".  "15 kg weight loss sustained over 6 months".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Goal.outcomeReference</t>
@@ -1245,7 +1245,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="118.27734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="40.328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="41.1796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-goal.xlsx
+++ b/fhir/StructureDefinition-ehealth-goal.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-goal.xlsx
+++ b/fhir/StructureDefinition-ehealth-goal.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-goal.xlsx
+++ b/fhir/StructureDefinition-ehealth-goal.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-goal.xlsx
+++ b/fhir/StructureDefinition-ehealth-goal.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-goal.xlsx
+++ b/fhir/StructureDefinition-ehealth-goal.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-goal.xlsx
+++ b/fhir/StructureDefinition-ehealth-goal.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
